--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OHIO_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OHIO_2012.xlsx
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C113">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C427">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C489">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C516">
